--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2179" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FC1C763-DC2D-4F32-ACC4-F80FCE77028F}"/>
+  <xr:revisionPtr revIDLastSave="2183" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F85EA8C7-1425-4E88-A2B2-D9203A800DE9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4886,10 +4886,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
@@ -37183,26 +37179,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -37437,10 +37413,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0065C2A-D54D-4F3D-A68A-F49590152888}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -37457,20 +37464,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0065C2A-D54D-4F3D-A68A-F49590152888}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -37179,26 +37179,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -37433,10 +37413,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0065C2A-D54D-4F3D-A68A-F49590152888}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -37453,20 +37464,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0065C2A-D54D-4F3D-A68A-F49590152888}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2183" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F85EA8C7-1425-4E88-A2B2-D9203A800DE9}"/>
+  <xr:revisionPtr revIDLastSave="2184" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD558F55-0728-4FC4-AE82-EF8F9BC11E43}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36165,6 +36165,7 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <autoFilter ref="A1:V578" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A109">
     <cfRule type="duplicateValues" dxfId="86" priority="89"/>
   </conditionalFormatting>
@@ -37179,6 +37180,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -37413,27 +37434,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0065C2A-D54D-4F3D-A68A-F49590152888}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -37450,23 +37470,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>